--- a/data/gated_research/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/gated_research/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1080,8 +1080,220 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>dadeed8a0aa84e7a</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1067-2026:179469</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.639939</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.1497429215686275</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:21.022990Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>098546fcb15446ef</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.756798</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.10644834965034966</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:31.074598Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ5"/>
+  <autoFilter ref="A1:AJ7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/gated_research/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1292,8 +1292,750 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>cc97cac2f80143f6</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1067-2026:179469</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.639939</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.1497429215686275</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:41:00.676654Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8e04d33717bb46cf</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.756798</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.10644834965034966</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:41:11.213709Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>02f75ff0c33a44b2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1067-2026:179469</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.639939</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.1497429215686275</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:46.960029Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>7e6efe178f7b447b</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.756798</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.10644834965034966</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:57.265599Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>4560d038e2f94328</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181785</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.561017</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.07082092156862746</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:12.259620Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>86ff13b661b14d96</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181836</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.567487</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.07729092156862744</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:10.755068Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ced34f3d42f2449f</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.57909</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.08889392156862747</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:20.160476Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ7"/>
+  <autoFilter ref="A1:AJ14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>